--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/51.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/51.xlsx
@@ -426,13 +426,13 @@
         <v>-15.21050417296596</v>
       </c>
       <c r="E2">
-        <v>-16.93740067983311</v>
+        <v>-16.06573299340075</v>
       </c>
       <c r="F2">
-        <v>2.410983887785523</v>
+        <v>1.194715224542288</v>
       </c>
       <c r="G2">
-        <v>-13.47895657428099</v>
+        <v>-13.13514761907728</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-15.08077746246988</v>
       </c>
       <c r="E3">
-        <v>-17.38037389331668</v>
+        <v>-17.3997984626829</v>
       </c>
       <c r="F3">
-        <v>2.103631416855212</v>
+        <v>1.481058641402798</v>
       </c>
       <c r="G3">
-        <v>-14.72196079230053</v>
+        <v>-13.44398695585532</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-14.80752601610853</v>
       </c>
       <c r="E4">
-        <v>-17.96202698614759</v>
+        <v>-17.17818725960137</v>
       </c>
       <c r="F4">
-        <v>2.809657237935258</v>
+        <v>1.232697526695451</v>
       </c>
       <c r="G4">
-        <v>-13.56961729095199</v>
+        <v>-13.158263151687</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-14.38258359302227</v>
       </c>
       <c r="E5">
-        <v>-19.39490150605874</v>
+        <v>-18.22983020558386</v>
       </c>
       <c r="F5">
-        <v>2.084207857994369</v>
+        <v>1.261667191506155</v>
       </c>
       <c r="G5">
-        <v>-13.43406090491991</v>
+        <v>-13.08078277908423</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-13.7955447318034</v>
       </c>
       <c r="E6">
-        <v>-18.19988139872052</v>
+        <v>-19.31853640942911</v>
       </c>
       <c r="F6">
-        <v>2.445213685604005</v>
+        <v>1.745553039647069</v>
       </c>
       <c r="G6">
-        <v>-12.78871094944262</v>
+        <v>-12.88289486593933</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-13.05920304521076</v>
       </c>
       <c r="E7">
-        <v>-20.4410705195151</v>
+        <v>-19.30460653864564</v>
       </c>
       <c r="F7">
-        <v>2.430004860088606</v>
+        <v>1.462196715641054</v>
       </c>
       <c r="G7">
-        <v>-13.12112400450612</v>
+        <v>-12.70047039300758</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-12.16879457882422</v>
       </c>
       <c r="E8">
-        <v>-20.87357348724877</v>
+        <v>-19.66828248830425</v>
       </c>
       <c r="F8">
-        <v>2.153875213304613</v>
+        <v>1.642156220429635</v>
       </c>
       <c r="G8">
-        <v>-12.90197679815577</v>
+        <v>-12.23781120641033</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-11.14578925698158</v>
       </c>
       <c r="E9">
-        <v>-21.46025196578272</v>
+        <v>-20.33543358946808</v>
       </c>
       <c r="F9">
-        <v>2.66788712715054</v>
+        <v>1.511863968378106</v>
       </c>
       <c r="G9">
-        <v>-11.6278420616318</v>
+        <v>-11.49809588768724</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-10.00510048493737</v>
       </c>
       <c r="E10">
-        <v>-21.80441612863729</v>
+        <v>-21.17543719275995</v>
       </c>
       <c r="F10">
-        <v>2.660763167486464</v>
+        <v>1.719764305663115</v>
       </c>
       <c r="G10">
-        <v>-10.95384440575622</v>
+        <v>-11.3783057882409</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-8.773900919597935</v>
       </c>
       <c r="E11">
-        <v>-20.45382918470497</v>
+        <v>-21.99089116391076</v>
       </c>
       <c r="F11">
-        <v>3.361066626547971</v>
+        <v>1.798595061183127</v>
       </c>
       <c r="G11">
-        <v>-10.91733053190491</v>
+        <v>-10.54603565764596</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-7.494061043309054</v>
       </c>
       <c r="E12">
-        <v>-21.57376338450161</v>
+        <v>-22.42335259953119</v>
       </c>
       <c r="F12">
-        <v>3.004310323714697</v>
+        <v>1.939694194371578</v>
       </c>
       <c r="G12">
-        <v>-10.45336075152292</v>
+        <v>-10.19692166943311</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-6.193492318188334</v>
       </c>
       <c r="E13">
-        <v>-24.2015791007358</v>
+        <v>-24.16547523468907</v>
       </c>
       <c r="F13">
-        <v>3.243628979853086</v>
+        <v>1.87923994131527</v>
       </c>
       <c r="G13">
-        <v>-10.06442768680641</v>
+        <v>-9.502359178413332</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-4.928248997588652</v>
       </c>
       <c r="E14">
-        <v>-23.30443561603694</v>
+        <v>-24.37931577938184</v>
       </c>
       <c r="F14">
-        <v>3.463353433445655</v>
+        <v>2.333107411513536</v>
       </c>
       <c r="G14">
-        <v>-9.413790973532111</v>
+        <v>-8.796960791968138</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-3.722280736454472</v>
       </c>
       <c r="E15">
-        <v>-26.16066964871405</v>
+        <v>-25.27665031180164</v>
       </c>
       <c r="F15">
-        <v>2.562860080884396</v>
+        <v>2.316036416076644</v>
       </c>
       <c r="G15">
-        <v>-8.436385635000301</v>
+        <v>-8.626736328510665</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-2.609535283182446</v>
       </c>
       <c r="E16">
-        <v>-25.58282089745668</v>
+        <v>-26.25763467351482</v>
       </c>
       <c r="F16">
-        <v>3.615713393107762</v>
+        <v>2.260630233972996</v>
       </c>
       <c r="G16">
-        <v>-7.988635105390598</v>
+        <v>-7.512987464452555</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-1.602758668141406</v>
       </c>
       <c r="E17">
-        <v>-26.99331376153832</v>
+        <v>-26.95798239279801</v>
       </c>
       <c r="F17">
-        <v>3.319177743723206</v>
+        <v>2.46500503959169</v>
       </c>
       <c r="G17">
-        <v>-6.999631534012768</v>
+        <v>-7.131346209379024</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-0.7034793719316771</v>
       </c>
       <c r="E18">
-        <v>-28.63096859563713</v>
+        <v>-27.11494886160858</v>
       </c>
       <c r="F18">
-        <v>3.261548223510445</v>
+        <v>2.669575339917445</v>
       </c>
       <c r="G18">
-        <v>-6.572947102508759</v>
+        <v>-6.459878365012234</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>0.0840549127907349</v>
       </c>
       <c r="E19">
-        <v>-29.26125994629311</v>
+        <v>-27.90721130072155</v>
       </c>
       <c r="F19">
-        <v>3.465155960914146</v>
+        <v>2.68831301056877</v>
       </c>
       <c r="G19">
-        <v>-5.874076882913644</v>
+        <v>-6.19403146478835</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>0.7777827007803663</v>
       </c>
       <c r="E20">
-        <v>-28.54678300208285</v>
+        <v>-29.6074778721478</v>
       </c>
       <c r="F20">
-        <v>3.51862873349966</v>
+        <v>2.998130702889813</v>
       </c>
       <c r="G20">
-        <v>-6.029301313322875</v>
+        <v>-5.501896966238307</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>1.374825312636442</v>
       </c>
       <c r="E21">
-        <v>-29.81813705696576</v>
+        <v>-29.51710814693086</v>
       </c>
       <c r="F21">
-        <v>3.862001932573305</v>
+        <v>2.827677542415759</v>
       </c>
       <c r="G21">
-        <v>-4.614024502714137</v>
+        <v>-5.464226532533133</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>1.886108490231108</v>
       </c>
       <c r="E22">
-        <v>-30.00828976086737</v>
+        <v>-30.40769371094782</v>
       </c>
       <c r="F22">
-        <v>3.954300285328032</v>
+        <v>3.15061491766234</v>
       </c>
       <c r="G22">
-        <v>-4.550680006699955</v>
+        <v>-5.366717832799643</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>2.306190948727315</v>
       </c>
       <c r="E23">
-        <v>-29.81966128552197</v>
+        <v>-30.30861885479403</v>
       </c>
       <c r="F23">
-        <v>4.519217032810793</v>
+        <v>3.02522825737019</v>
       </c>
       <c r="G23">
-        <v>-3.991521173153675</v>
+        <v>-4.628404483921988</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>2.628264547463731</v>
       </c>
       <c r="E24">
-        <v>-31.62975745382765</v>
+        <v>-31.17941852005951</v>
       </c>
       <c r="F24">
-        <v>3.461920357838811</v>
+        <v>3.263229809338128</v>
       </c>
       <c r="G24">
-        <v>-3.931064160657265</v>
+        <v>-4.333865500641769</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>2.841411892505711</v>
       </c>
       <c r="E25">
-        <v>-32.58779532297115</v>
+        <v>-31.69831866637792</v>
       </c>
       <c r="F25">
-        <v>3.898822863627744</v>
+        <v>3.090781940158132</v>
       </c>
       <c r="G25">
-        <v>-3.482224950553069</v>
+        <v>-4.521831278968153</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>2.931681453739991</v>
       </c>
       <c r="E26">
-        <v>-32.6263682731505</v>
+        <v>-31.32194427309365</v>
       </c>
       <c r="F26">
-        <v>4.113136421345226</v>
+        <v>3.377410315405206</v>
       </c>
       <c r="G26">
-        <v>-4.692435605763633</v>
+        <v>-4.208646357818203</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>2.888116868733506</v>
       </c>
       <c r="E27">
-        <v>-34.35049296703223</v>
+        <v>-31.64512848894084</v>
       </c>
       <c r="F27">
-        <v>4.097125736183917</v>
+        <v>2.835918141338808</v>
       </c>
       <c r="G27">
-        <v>-5.065879122821069</v>
+        <v>-4.561684295151498</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>2.703671987503972</v>
       </c>
       <c r="E28">
-        <v>-32.3597321060965</v>
+        <v>-31.57236837974117</v>
       </c>
       <c r="F28">
-        <v>4.307494608329268</v>
+        <v>3.118414619980718</v>
       </c>
       <c r="G28">
-        <v>-2.723887190661575</v>
+        <v>-4.194676263511156</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>2.378935136752225</v>
       </c>
       <c r="E29">
-        <v>-32.49972855343383</v>
+        <v>-31.82354214103283</v>
       </c>
       <c r="F29">
-        <v>3.812652772918927</v>
+        <v>3.219013214111496</v>
       </c>
       <c r="G29">
-        <v>-3.768952586016677</v>
+        <v>-4.374587894773954</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>1.920208390777005</v>
       </c>
       <c r="E30">
-        <v>-32.2112984099528</v>
+        <v>-31.51144076960594</v>
       </c>
       <c r="F30">
-        <v>4.086294004024911</v>
+        <v>2.899157365603328</v>
       </c>
       <c r="G30">
-        <v>-4.274486725661489</v>
+        <v>-4.575816255623193</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>1.342879113886635</v>
       </c>
       <c r="E31">
-        <v>-31.84984858156429</v>
+        <v>-31.34539122762797</v>
       </c>
       <c r="F31">
-        <v>3.512949446586067</v>
+        <v>3.106486129380405</v>
       </c>
       <c r="G31">
-        <v>-4.455484426674191</v>
+        <v>-4.820735427204713</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>0.66323925767954</v>
       </c>
       <c r="E32">
-        <v>-30.82992786368085</v>
+        <v>-31.15906363135652</v>
       </c>
       <c r="F32">
-        <v>4.234863354451807</v>
+        <v>3.476657013934615</v>
       </c>
       <c r="G32">
-        <v>-3.901453095504858</v>
+        <v>-4.691861241953588</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-0.08896935323325912</v>
       </c>
       <c r="E33">
-        <v>-32.26912564783404</v>
+        <v>-30.9165015537469</v>
       </c>
       <c r="F33">
-        <v>4.154135637579385</v>
+        <v>3.279565214521334</v>
       </c>
       <c r="G33">
-        <v>-3.829756827543705</v>
+        <v>-4.978789904750712</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-0.8914393333996686</v>
       </c>
       <c r="E34">
-        <v>-31.25989944911203</v>
+        <v>-31.18706873531984</v>
       </c>
       <c r="F34">
-        <v>4.487558487410602</v>
+        <v>3.111883771377046</v>
       </c>
       <c r="G34">
-        <v>-4.017349269393559</v>
+        <v>-5.20356196032261</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-1.707742466778488</v>
       </c>
       <c r="E35">
-        <v>-31.58003520784681</v>
+        <v>-30.81019180346526</v>
       </c>
       <c r="F35">
-        <v>4.517517222900249</v>
+        <v>3.208579098305833</v>
       </c>
       <c r="G35">
-        <v>-4.270544501328908</v>
+        <v>-5.609532744240726</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-2.507610563105499</v>
       </c>
       <c r="E36">
-        <v>-31.24890797534088</v>
+        <v>-29.83635927165344</v>
       </c>
       <c r="F36">
-        <v>5.254056785629818</v>
+        <v>3.340485010058015</v>
       </c>
       <c r="G36">
-        <v>-4.660284286124073</v>
+        <v>-5.256001376179711</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-3.260680267542725</v>
       </c>
       <c r="E37">
-        <v>-30.79691814007111</v>
+        <v>-29.79322194222811</v>
       </c>
       <c r="F37">
-        <v>4.413739354677527</v>
+        <v>3.454914026345933</v>
       </c>
       <c r="G37">
-        <v>-4.587992768396146</v>
+        <v>-5.808220850602811</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-3.937528070697973</v>
       </c>
       <c r="E38">
-        <v>-29.17258680790236</v>
+        <v>-29.54642981888415</v>
       </c>
       <c r="F38">
-        <v>3.900925260096049</v>
+        <v>3.410185500064371</v>
       </c>
       <c r="G38">
-        <v>-4.621026519707502</v>
+        <v>-5.718826345058501</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-4.523705963876111</v>
       </c>
       <c r="E39">
-        <v>-30.13928827586945</v>
+        <v>-28.31093043736849</v>
       </c>
       <c r="F39">
-        <v>4.618809988914573</v>
+        <v>3.627120012244311</v>
       </c>
       <c r="G39">
-        <v>-5.333725853401745</v>
+        <v>-5.979496138758207</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-5.001722198667334</v>
       </c>
       <c r="E40">
-        <v>-28.67695710463695</v>
+        <v>-28.42674688837266</v>
       </c>
       <c r="F40">
-        <v>4.300022734356017</v>
+        <v>3.721573776981122</v>
       </c>
       <c r="G40">
-        <v>-6.206782341371348</v>
+        <v>-6.194637157533489</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-5.375962693578913</v>
       </c>
       <c r="E41">
-        <v>-28.36044294617743</v>
+        <v>-28.40424271280908</v>
       </c>
       <c r="F41">
-        <v>5.142114528285105</v>
+        <v>3.909210590858849</v>
       </c>
       <c r="G41">
-        <v>-5.5864198223756</v>
+        <v>-6.408950570273387</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-5.648323039892885</v>
       </c>
       <c r="E42">
-        <v>-29.18714796680721</v>
+        <v>-27.19594478886538</v>
       </c>
       <c r="F42">
-        <v>4.555794423848809</v>
+        <v>3.525924993583518</v>
       </c>
       <c r="G42">
-        <v>-4.938571384324611</v>
+        <v>-6.326307450241696</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-5.831207643417538</v>
       </c>
       <c r="E43">
-        <v>-28.91520399568008</v>
+        <v>-26.21791751361548</v>
       </c>
       <c r="F43">
-        <v>4.782347938310057</v>
+        <v>4.041073427506086</v>
       </c>
       <c r="G43">
-        <v>-5.587902725303352</v>
+        <v>-6.705619921139954</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-5.941974249150884</v>
       </c>
       <c r="E44">
-        <v>-27.323261482028</v>
+        <v>-26.21361063347164</v>
       </c>
       <c r="F44">
-        <v>5.174664397010709</v>
+        <v>4.145919889678419</v>
       </c>
       <c r="G44">
-        <v>-5.986579088833897</v>
+        <v>-6.716945331176204</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-5.995974329262725</v>
       </c>
       <c r="E45">
-        <v>-25.8603509378157</v>
+        <v>-25.41741510323406</v>
       </c>
       <c r="F45">
-        <v>5.363573583219136</v>
+        <v>4.064488060513616</v>
       </c>
       <c r="G45">
-        <v>-6.874678687137495</v>
+        <v>-6.890444973723228</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-6.017040249321187</v>
       </c>
       <c r="E46">
-        <v>-25.02740364056471</v>
+        <v>-25.23815834924313</v>
       </c>
       <c r="F46">
-        <v>5.140795767379847</v>
+        <v>4.236437252517127</v>
       </c>
       <c r="G46">
-        <v>-6.375666187481284</v>
+        <v>-6.963464889192076</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-6.019799242858339</v>
       </c>
       <c r="E47">
-        <v>-27.26778703836227</v>
+        <v>-24.58166854155013</v>
       </c>
       <c r="F47">
-        <v>4.946462431417889</v>
+        <v>4.392384043033356</v>
       </c>
       <c r="G47">
-        <v>-6.332325216524212</v>
+        <v>-7.05648049748426</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-6.023095137124656</v>
       </c>
       <c r="E48">
-        <v>-24.98644467047925</v>
+        <v>-24.54538608741643</v>
       </c>
       <c r="F48">
-        <v>4.953182147789398</v>
+        <v>4.215481213961104</v>
       </c>
       <c r="G48">
-        <v>-7.341735672998479</v>
+        <v>-7.236316417153916</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-6.03867751387071</v>
       </c>
       <c r="E49">
-        <v>-24.01544878200228</v>
+        <v>-23.75107611512032</v>
       </c>
       <c r="F49">
-        <v>5.486943997252872</v>
+        <v>4.090869905557975</v>
       </c>
       <c r="G49">
-        <v>-6.224527572357144</v>
+        <v>-6.867726274291361</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-6.072805681631992</v>
       </c>
       <c r="E50">
-        <v>-23.37632770406972</v>
+        <v>-23.27156294840092</v>
       </c>
       <c r="F50">
-        <v>4.679429915451441</v>
+        <v>4.262824067765902</v>
       </c>
       <c r="G50">
-        <v>-6.58528287070177</v>
+        <v>-7.338952619264353</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-6.134271679988705</v>
       </c>
       <c r="E51">
-        <v>-22.55836519327871</v>
+        <v>-22.77436956107172</v>
       </c>
       <c r="F51">
-        <v>5.954396692857049</v>
+        <v>4.376042010910927</v>
       </c>
       <c r="G51">
-        <v>-6.744817640430929</v>
+        <v>-7.427989452799681</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-6.222540907864622</v>
       </c>
       <c r="E52">
-        <v>-23.16386187232547</v>
+        <v>-21.9045666665242</v>
       </c>
       <c r="F52">
-        <v>5.205859056665332</v>
+        <v>4.174636074063867</v>
       </c>
       <c r="G52">
-        <v>-7.734172356956264</v>
+        <v>-7.662183685600906</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-6.342141852971822</v>
       </c>
       <c r="E53">
-        <v>-21.60158574716664</v>
+        <v>-21.39304054691302</v>
       </c>
       <c r="F53">
-        <v>5.245271120955727</v>
+        <v>4.392251504248908</v>
       </c>
       <c r="G53">
-        <v>-5.886363046959422</v>
+        <v>-7.429323543285739</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-6.491031027458053</v>
       </c>
       <c r="E54">
-        <v>-22.92741124518033</v>
+        <v>-20.54922014241363</v>
       </c>
       <c r="F54">
-        <v>5.089627512908923</v>
+        <v>4.084882465970541</v>
       </c>
       <c r="G54">
-        <v>-7.218284004263096</v>
+        <v>-7.645908303819906</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-6.672389964772075</v>
       </c>
       <c r="E55">
-        <v>-21.23391440821354</v>
+        <v>-20.44015681302363</v>
       </c>
       <c r="F55">
-        <v>5.030200435432086</v>
+        <v>4.307994942240559</v>
       </c>
       <c r="G55">
-        <v>-7.029378357883913</v>
+        <v>-7.743619336259208</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-6.889909516196471</v>
       </c>
       <c r="E56">
-        <v>-21.83663674209531</v>
+        <v>-19.53061599252016</v>
       </c>
       <c r="F56">
-        <v>4.851418869090285</v>
+        <v>4.263289610246275</v>
       </c>
       <c r="G56">
-        <v>-8.096410558228641</v>
+        <v>-8.30849700583232</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-7.143300209279032</v>
       </c>
       <c r="E57">
-        <v>-19.44501415390412</v>
+        <v>-18.38990742967673</v>
       </c>
       <c r="F57">
-        <v>4.875749676445312</v>
+        <v>4.193373744715192</v>
       </c>
       <c r="G57">
-        <v>-7.667415617761497</v>
+        <v>-8.150956844970771</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-7.440913588423031</v>
       </c>
       <c r="E58">
-        <v>-19.73848837253915</v>
+        <v>-18.5643713777988</v>
       </c>
       <c r="F58">
-        <v>5.149530073274966</v>
+        <v>4.259323387121672</v>
       </c>
       <c r="G58">
-        <v>-7.263953759395442</v>
+        <v>-8.174121981727719</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-7.780108318826678</v>
       </c>
       <c r="E59">
-        <v>-19.16348457103929</v>
+        <v>-18.54724768750653</v>
       </c>
       <c r="F59">
-        <v>4.364837513420661</v>
+        <v>4.245608936400923</v>
       </c>
       <c r="G59">
-        <v>-7.969500958282329</v>
+        <v>-8.005454827418845</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-8.167332275718643</v>
       </c>
       <c r="E60">
-        <v>-16.3320618228167</v>
+        <v>-17.51853462124842</v>
       </c>
       <c r="F60">
-        <v>5.686474510299994</v>
+        <v>4.194480443565332</v>
       </c>
       <c r="G60">
-        <v>-7.669968925971606</v>
+        <v>-8.775713247113362</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-8.59759174856233</v>
       </c>
       <c r="E61">
-        <v>-18.64087353040214</v>
+        <v>-16.97742102415916</v>
       </c>
       <c r="F61">
-        <v>4.696895213772065</v>
+        <v>4.020046149353423</v>
       </c>
       <c r="G61">
-        <v>-7.86643659405895</v>
+        <v>-8.151881048556026</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-9.068950948344943</v>
       </c>
       <c r="E62">
-        <v>-16.95335731774311</v>
+        <v>-16.36008769283665</v>
       </c>
       <c r="F62">
-        <v>4.722427153861152</v>
+        <v>4.005198492025644</v>
       </c>
       <c r="G62">
-        <v>-7.72759589133125</v>
+        <v>-8.569309085112241</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-9.575413735509336</v>
       </c>
       <c r="E63">
-        <v>-18.09545305316903</v>
+        <v>-16.20702524267142</v>
       </c>
       <c r="F63">
-        <v>4.936510425440656</v>
+        <v>3.696866890825224</v>
       </c>
       <c r="G63">
-        <v>-8.670226111909431</v>
+        <v>-8.923024510666931</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-10.10149191528328</v>
       </c>
       <c r="E64">
-        <v>-17.02106296876046</v>
+        <v>-16.75483796962763</v>
       </c>
       <c r="F64">
-        <v>5.096632187666994</v>
+        <v>3.920087054857607</v>
       </c>
       <c r="G64">
-        <v>-9.170640581411069</v>
+        <v>-8.494123557005066</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-10.63930873670444</v>
       </c>
       <c r="E65">
-        <v>-17.27105721803586</v>
+        <v>-14.7157939504351</v>
       </c>
       <c r="F65">
-        <v>5.23382971038826</v>
+        <v>3.534861421124919</v>
       </c>
       <c r="G65">
-        <v>-9.537768707302602</v>
+        <v>-9.233575190524446</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-11.16686945728644</v>
       </c>
       <c r="E66">
-        <v>-17.35226495907024</v>
+        <v>-15.26914290808731</v>
       </c>
       <c r="F66">
-        <v>4.67985569629648</v>
+        <v>3.284258744225596</v>
       </c>
       <c r="G66">
-        <v>-8.756362408204032</v>
+        <v>-8.617588279463405</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-11.67364127024188</v>
       </c>
       <c r="E67">
-        <v>-16.14356417362804</v>
+        <v>-14.92945590704091</v>
       </c>
       <c r="F67">
-        <v>4.981901645644458</v>
+        <v>3.464822957218221</v>
       </c>
       <c r="G67">
-        <v>-8.666657224053379</v>
+        <v>-8.908649750948261</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-12.14236992948908</v>
       </c>
       <c r="E68">
-        <v>-15.83954495143926</v>
+        <v>-15.33202668075654</v>
       </c>
       <c r="F68">
-        <v>4.367069135203803</v>
+        <v>3.246152186962013</v>
       </c>
       <c r="G68">
-        <v>-8.91934336079346</v>
+        <v>-8.742170400606739</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-12.55998851483278</v>
       </c>
       <c r="E69">
-        <v>-14.30975939847457</v>
+        <v>-14.52251595501156</v>
       </c>
       <c r="F69">
-        <v>4.478817554576262</v>
+        <v>3.502379478526345</v>
       </c>
       <c r="G69">
-        <v>-9.155615746289213</v>
+        <v>-8.505540343102004</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-12.91843592554454</v>
       </c>
       <c r="E70">
-        <v>-14.94881817823726</v>
+        <v>-15.28914477382768</v>
       </c>
       <c r="F70">
-        <v>3.960320859611579</v>
+        <v>3.314209196041215</v>
       </c>
       <c r="G70">
-        <v>-9.274371990877478</v>
+        <v>-8.832524354788283</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-13.20370479220291</v>
       </c>
       <c r="E71">
-        <v>-14.84146597191309</v>
+        <v>-14.51597049396363</v>
       </c>
       <c r="F71">
-        <v>3.824682324342382</v>
+        <v>3.144938944218358</v>
       </c>
       <c r="G71">
-        <v>-8.819871381127452</v>
+        <v>-8.513345164057137</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-13.41274780067592</v>
       </c>
       <c r="E72">
-        <v>-16.65286001875779</v>
+        <v>-14.96987080644281</v>
       </c>
       <c r="F72">
-        <v>4.216702227512831</v>
+        <v>3.135126103964795</v>
       </c>
       <c r="G72">
-        <v>-8.422820206104875</v>
+        <v>-8.652920791387237</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-13.53489782434894</v>
       </c>
       <c r="E73">
-        <v>-16.31857634564499</v>
+        <v>-14.98031613292476</v>
       </c>
       <c r="F73">
-        <v>3.595131776617805</v>
+        <v>3.196698653014882</v>
       </c>
       <c r="G73">
-        <v>-8.064260543961376</v>
+        <v>-8.646487916714733</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-13.56640518997018</v>
       </c>
       <c r="E74">
-        <v>-16.4279760851523</v>
+        <v>-14.975639616973</v>
       </c>
       <c r="F74">
-        <v>4.262013924445964</v>
+        <v>2.951553260565202</v>
       </c>
       <c r="G74">
-        <v>-8.23598618555874</v>
+        <v>-8.315501633570276</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-13.50794901780837</v>
       </c>
       <c r="E75">
-        <v>-17.51605930729882</v>
+        <v>-14.82097402723639</v>
       </c>
       <c r="F75">
-        <v>3.839433891051435</v>
+        <v>2.963584468723462</v>
       </c>
       <c r="G75">
-        <v>-8.404123358715617</v>
+        <v>-7.868667475312056</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-13.35651817546508</v>
       </c>
       <c r="E76">
-        <v>-17.81416850977237</v>
+        <v>-15.51063138056947</v>
       </c>
       <c r="F76">
-        <v>3.364847295374348</v>
+        <v>2.930371906075619</v>
       </c>
       <c r="G76">
-        <v>-8.450124678411035</v>
+        <v>-8.02721668895807</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-13.11935279879649</v>
       </c>
       <c r="E77">
-        <v>-15.2858180515565</v>
+        <v>-15.10154421828518</v>
       </c>
       <c r="F77">
-        <v>3.724731513520594</v>
+        <v>2.888769638372222</v>
       </c>
       <c r="G77">
-        <v>-7.953913507701087</v>
+        <v>-7.939058370977652</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-12.79670559915032</v>
       </c>
       <c r="E78">
-        <v>-16.25723756758859</v>
+        <v>-15.23005703630935</v>
       </c>
       <c r="F78">
-        <v>3.423747531183004</v>
+        <v>2.702010893941463</v>
       </c>
       <c r="G78">
-        <v>-7.613657775885883</v>
+        <v>-8.116709097424547</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-12.39451681679402</v>
       </c>
       <c r="E79">
-        <v>-17.40034253336645</v>
+        <v>-16.01638453643914</v>
       </c>
       <c r="F79">
-        <v>3.723266959952444</v>
+        <v>2.763843550356029</v>
       </c>
       <c r="G79">
-        <v>-7.83802777679075</v>
+        <v>-7.520349764199495</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-11.92045145369502</v>
       </c>
       <c r="E80">
-        <v>-17.79204019983368</v>
+        <v>-17.11451852999175</v>
       </c>
       <c r="F80">
-        <v>3.144912436461468</v>
+        <v>2.525515621631389</v>
       </c>
       <c r="G80">
-        <v>-7.752367941384028</v>
+        <v>-6.8349875371188</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-11.3752273153465</v>
       </c>
       <c r="E81">
-        <v>-19.14322520619677</v>
+        <v>-17.27913521406266</v>
       </c>
       <c r="F81">
-        <v>3.389209580690682</v>
+        <v>2.593493107439921</v>
       </c>
       <c r="G81">
-        <v>-6.659597715487809</v>
+        <v>-6.920262287698333</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-10.77331192531128</v>
       </c>
       <c r="E82">
-        <v>-18.1487761333685</v>
+        <v>-18.20051684005322</v>
       </c>
       <c r="F82">
-        <v>3.129634028084234</v>
+        <v>2.409126688068447</v>
       </c>
       <c r="G82">
-        <v>-6.564793747150713</v>
+        <v>-6.755746217289329</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-10.11492184958964</v>
       </c>
       <c r="E83">
-        <v>-18.58143692313252</v>
+        <v>-18.32559910552308</v>
       </c>
       <c r="F83">
-        <v>3.399676831192457</v>
+        <v>2.26021108006718</v>
       </c>
       <c r="G83">
-        <v>-5.088407237897785</v>
+        <v>-6.41454017444296</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-9.412353147775979</v>
       </c>
       <c r="E84">
-        <v>-20.26266102063444</v>
+        <v>-19.07199763197597</v>
       </c>
       <c r="F84">
-        <v>3.490581869975674</v>
+        <v>2.410939155945772</v>
       </c>
       <c r="G84">
-        <v>-6.310394961958861</v>
+        <v>-6.181473783305095</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-8.673123074688629</v>
       </c>
       <c r="E85">
-        <v>-20.26389452439791</v>
+        <v>-21.24183458220999</v>
       </c>
       <c r="F85">
-        <v>3.382271175324833</v>
+        <v>2.185098037450932</v>
       </c>
       <c r="G85">
-        <v>-5.884018598316603</v>
+        <v>-5.612454167438181</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-7.905511633397738</v>
       </c>
       <c r="E86">
-        <v>-22.01111314985135</v>
+        <v>-21.27643498575713</v>
       </c>
       <c r="F86">
-        <v>2.96041182157074</v>
+        <v>2.221839445234701</v>
       </c>
       <c r="G86">
-        <v>-4.862115728973858</v>
+        <v>-5.401012573748507</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-7.12988833859068</v>
       </c>
       <c r="E87">
-        <v>-23.92078463627547</v>
+        <v>-22.44556397369637</v>
       </c>
       <c r="F87">
-        <v>3.226364146443938</v>
+        <v>2.224723820531249</v>
       </c>
       <c r="G87">
-        <v>-5.752507561028454</v>
+        <v>-5.42334488298089</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-6.355686958127062</v>
       </c>
       <c r="E88">
-        <v>-24.69062388744569</v>
+        <v>-23.65526152985653</v>
       </c>
       <c r="F88">
-        <v>3.11703621662246</v>
+        <v>1.924879671739912</v>
       </c>
       <c r="G88">
-        <v>-5.891511435293098</v>
+        <v>-5.388460113754435</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-5.61113692182869</v>
       </c>
       <c r="E89">
-        <v>-25.78994154622588</v>
+        <v>-25.05075299463289</v>
       </c>
       <c r="F89">
-        <v>3.067643981863136</v>
+        <v>1.981879632726546</v>
       </c>
       <c r="G89">
-        <v>-4.977270451398684</v>
+        <v>-5.171710876311027</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-4.910497772851132</v>
       </c>
       <c r="E90">
-        <v>-27.51423444516627</v>
+        <v>-26.05985044380384</v>
       </c>
       <c r="F90">
-        <v>3.029507603373053</v>
+        <v>1.712312312507531</v>
       </c>
       <c r="G90">
-        <v>-3.793386544644906</v>
+        <v>-5.021407699456044</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-4.276426782023535</v>
       </c>
       <c r="E91">
-        <v>-28.38132321611301</v>
+        <v>-27.90867323110788</v>
       </c>
       <c r="F91">
-        <v>3.075622816686901</v>
+        <v>1.583338821361259</v>
       </c>
       <c r="G91">
-        <v>-4.925136492658742</v>
+        <v>-5.245386088672245</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-3.724596052461985</v>
       </c>
       <c r="E92">
-        <v>-30.23758440489983</v>
+        <v>-29.05812638039574</v>
       </c>
       <c r="F92">
-        <v>3.308640910359596</v>
+        <v>1.633663797816134</v>
       </c>
       <c r="G92">
-        <v>-4.627702193626979</v>
+        <v>-4.50505724497025</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-3.261383049565685</v>
       </c>
       <c r="E93">
-        <v>-30.09561310557755</v>
+        <v>-31.24267400514231</v>
       </c>
       <c r="F93">
-        <v>3.11953954291372</v>
+        <v>1.48435554366594</v>
       </c>
       <c r="G93">
-        <v>-4.216037375755644</v>
+        <v>-4.742535794467097</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-2.895051330123971</v>
       </c>
       <c r="E94">
-        <v>-33.56333274803182</v>
+        <v>-32.51755413643999</v>
       </c>
       <c r="F94">
-        <v>2.506802802002148</v>
+        <v>1.140278232299915</v>
       </c>
       <c r="G94">
-        <v>-4.851884220921286</v>
+        <v>-4.641643569743524</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-2.614149044530528</v>
       </c>
       <c r="E95">
-        <v>-34.69953092337649</v>
+        <v>-35.06455251350434</v>
       </c>
       <c r="F95">
-        <v>2.214157165941138</v>
+        <v>0.9020082892934711</v>
       </c>
       <c r="G95">
-        <v>-4.196323643348149</v>
+        <v>-4.873550790282935</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-2.411827342957806</v>
       </c>
       <c r="E96">
-        <v>-38.22965048938064</v>
+        <v>-36.89073406927109</v>
       </c>
       <c r="F96">
-        <v>2.013599477314544</v>
+        <v>0.6781801035874335</v>
       </c>
       <c r="G96">
-        <v>-4.029191606858849</v>
+        <v>-4.680235596289361</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-2.266549197653775</v>
       </c>
       <c r="E97">
-        <v>-39.34596101229636</v>
+        <v>-38.86845384664685</v>
       </c>
       <c r="F97">
-        <v>2.175369690672454</v>
+        <v>0.6616972490065289</v>
       </c>
       <c r="G97">
-        <v>-4.384250260505665</v>
+        <v>-5.187174316524191</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-2.159484428785671</v>
       </c>
       <c r="E98">
-        <v>-43.12672688175392</v>
+        <v>-40.72381171197052</v>
       </c>
       <c r="F98">
-        <v>1.323692029158171</v>
+        <v>0.3970661701407961</v>
       </c>
       <c r="G98">
-        <v>-4.877286765792817</v>
+        <v>-5.793498861853523</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-2.071450896863548</v>
       </c>
       <c r="E99">
-        <v>-44.89176901360786</v>
+        <v>-43.26888715219147</v>
       </c>
       <c r="F99">
-        <v>0.713118983902711</v>
+        <v>0.4439964969789993</v>
       </c>
       <c r="G99">
-        <v>-4.464368790517749</v>
+        <v>-5.293982488491227</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-1.98223856435663</v>
       </c>
       <c r="E100">
-        <v>-46.81106764388293</v>
+        <v>-45.20611519575583</v>
       </c>
       <c r="F100">
-        <v>1.218375054301047</v>
+        <v>-0.02091062559637567</v>
       </c>
       <c r="G100">
-        <v>-4.862956388732197</v>
+        <v>-5.92333902260336</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-1.882968558503358</v>
       </c>
       <c r="E101">
-        <v>-49.36040116401467</v>
+        <v>-47.14323629412856</v>
       </c>
       <c r="F101">
-        <v>0.534884968414161</v>
+        <v>-0.3361698633864087</v>
       </c>
       <c r="G101">
-        <v>-5.565747946703165</v>
+        <v>-5.969329899320412</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-1.763386830568207</v>
       </c>
       <c r="E102">
-        <v>-48.41339110924142</v>
+        <v>-49.61134026886647</v>
       </c>
       <c r="F102">
-        <v>0.431677016964565</v>
+        <v>-0.5534001027291483</v>
       </c>
       <c r="G102">
-        <v>-5.952117260231202</v>
+        <v>-6.369708468324363</v>
       </c>
     </row>
   </sheetData>
